--- a/timeTable_ME.xlsx
+++ b/timeTable_ME.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3720" yWindow="4050" windowWidth="21705" windowHeight="8580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="4545" windowWidth="21705" windowHeight="8580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,18 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -53,27 +48,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -101,15 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -481,42 +458,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>week_day</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>slot_1</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>slot_2</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>slot_3</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>slot_4</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>slot_5</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>slot_6</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>slot_x</t>
         </is>
@@ -540,12 +517,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>GAPHT121(P)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>EZER</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -582,12 +559,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GMEST103(P)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZADIE</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -676,12 +653,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>GXESL106(P)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZADIE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
